--- a/research/PCT.NZ/Reports/PCT.NZ_DCF_Model.xlsx
+++ b/research/PCT.NZ/Reports/PCT.NZ_DCF_Model.xlsx
@@ -818,9 +818,10 @@
         <f>B19+B21*B20</f>
         <v/>
       </c>
-      <c r="F22" s="2">
-        <f> rf + beta x ERP = 9.40%</f>
-        <v/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>= rf + beta x ERP = 9.40%</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -908,9 +909,10 @@
         <f>B22+SUM(B23:B27)</f>
         <v/>
       </c>
-      <c r="F28" s="2">
-        <f> 10.25%. Cost of EQUITY, not WACC — debt cost already inside AFFO. Built in NZD off NZ rf, matching NZD flows and quote</f>
-        <v/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>= 10.25%. Cost of EQUITY, not WACC — debt cost already inside AFFO. Built in NZD off NZ rf, matching NZD flows and quote</t>
+        </is>
       </c>
     </row>
     <row r="30">
